--- a/stock_data.xlsx
+++ b/stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\SACHIN ITT\Day 13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC08C3E9-AD5B-4AEB-A158-5E50F11D9C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB23155-1B25-48DC-8F29-EA8E9776598C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Stock</t>
   </si>
@@ -55,6 +55,21 @@
   </si>
   <si>
     <t>INFY</t>
+  </si>
+  <si>
+    <t>HDFC</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>ROE</t>
+  </si>
+  <si>
+    <t>Debt</t>
   </si>
 </sst>
 </file>
@@ -386,10 +401,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -408,8 +423,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -428,385 +455,145 @@
       <c r="F2" s="2">
         <v>120000</v>
       </c>
+      <c r="G2" s="2">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2">
+        <v>28</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>192</v>
+        <v>3800</v>
       </c>
       <c r="C3" s="2">
-        <v>195</v>
+        <v>3850</v>
       </c>
       <c r="D3" s="2">
-        <v>189</v>
+        <v>3750</v>
       </c>
       <c r="E3" s="2">
-        <v>190</v>
+        <v>3780</v>
       </c>
       <c r="F3" s="2">
-        <v>130000</v>
+        <v>80000</v>
+      </c>
+      <c r="G3" s="2">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>188</v>
+        <v>2500</v>
       </c>
       <c r="C4" s="2">
-        <v>193</v>
+        <v>2550</v>
       </c>
       <c r="D4" s="2">
-        <v>187</v>
+        <v>2450</v>
       </c>
       <c r="E4" s="2">
-        <v>192</v>
+        <v>2480</v>
       </c>
       <c r="F4" s="2">
-        <v>125000</v>
+        <v>200000</v>
+      </c>
+      <c r="G4" s="2">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>195</v>
+        <v>1500</v>
       </c>
       <c r="C5" s="2">
-        <v>198</v>
+        <v>1520</v>
       </c>
       <c r="D5" s="2">
-        <v>191</v>
+        <v>1480</v>
       </c>
       <c r="E5" s="2">
-        <v>193</v>
+        <v>1490</v>
       </c>
       <c r="F5" s="2">
-        <v>140000</v>
+        <v>110000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2">
+        <v>30</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="C6" s="2">
-        <v>202</v>
+        <v>1620</v>
       </c>
       <c r="D6" s="2">
-        <v>194</v>
+        <v>1580</v>
       </c>
       <c r="E6" s="2">
-        <v>195</v>
+        <v>1590</v>
       </c>
       <c r="F6" s="2">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2">
-        <v>3800</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3850</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3750</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3780</v>
-      </c>
-      <c r="F7" s="2">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3820</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3900</v>
-      </c>
-      <c r="D8" s="2">
-        <v>3790</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3800</v>
-      </c>
-      <c r="F8" s="2">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3750</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3830</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3720</v>
-      </c>
-      <c r="E9" s="2">
-        <v>3820</v>
-      </c>
-      <c r="F9" s="2">
         <v>90000</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <v>3900</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3950</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3850</v>
-      </c>
-      <c r="E10" s="2">
-        <v>3880</v>
-      </c>
-      <c r="F10" s="2">
-        <v>95000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2">
-        <v>4000</v>
-      </c>
-      <c r="C11" s="2">
-        <v>4050</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3920</v>
-      </c>
-      <c r="E11" s="2">
-        <v>3950</v>
-      </c>
-      <c r="F11" s="2">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2500</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2550</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2450</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2480</v>
-      </c>
-      <c r="F12" s="2">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2520</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2580</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2490</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2500</v>
-      </c>
-      <c r="F13" s="2">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2450</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2520</v>
-      </c>
-      <c r="D14" s="2">
-        <v>2430</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2500</v>
-      </c>
-      <c r="F14" s="2">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2600</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2650</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2550</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2580</v>
-      </c>
-      <c r="F15" s="2">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2">
-        <v>2700</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2750</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2620</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2650</v>
-      </c>
-      <c r="F16" s="2">
-        <v>230000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="2">
-        <v>1500</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1520</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1480</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1490</v>
-      </c>
-      <c r="F17" s="2">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="2">
-        <v>1520</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1550</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1510</v>
-      </c>
-      <c r="F18" s="2">
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1480</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1510</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1460</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1500</v>
-      </c>
-      <c r="F19" s="2">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1550</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1580</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1520</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1530</v>
-      </c>
-      <c r="F20" s="2">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1600</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1620</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1560</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1580</v>
-      </c>
-      <c r="F21" s="2">
-        <v>130000</v>
+      <c r="G6" s="2">
+        <v>18</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
